--- a/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfd60ddbb42bf4c3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R28fd3bf7c47a4b58"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e58f26552d241f0"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R779111dd589548a4"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R28fd3bf7c47a4b58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1b07d2620b9a4506"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R779111dd589548a4"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91e8fb9440de4c8f"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1b07d2620b9a4506"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R83e0d36995e44c99"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91e8fb9440de4c8f"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra73f3b25642f4a19"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R83e0d36995e44c99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc9913622bb1a491a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra73f3b25642f4a19"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bf40c22e4f34ab5"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc9913622bb1a491a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3607d6891ab14354"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bf40c22e4f34ab5"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fafcfce8cf446ee"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3607d6891ab14354"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R73fdf95da1674a8b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fafcfce8cf446ee"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab42f68820c144ca"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R73fdf95da1674a8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfba4ee10952944a1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab42f68820c144ca"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20c37ec03f264069"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfba4ee10952944a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R045858f1a8574d8d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20c37ec03f264069"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02e0e55993bf441a"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R045858f1a8574d8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9a9d2ac17ad14d93"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02e0e55993bf441a"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc87f304cf95d4990"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9a9d2ac17ad14d93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3a5d270f1ad443d8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc87f304cf95d4990"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb184b7ebf15446fd"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3a5d270f1ad443d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0aab42b2a1d9401f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb184b7ebf15446fd"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16795c5b1f814451"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0aab42b2a1d9401f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R27f5ea7bd4ee4b17"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16795c5b1f814451"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R121ab52ef8f143bf"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R27f5ea7bd4ee4b17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R53550e1f477848f0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R121ab52ef8f143bf"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d44a6aefa6b4c5b"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R53550e1f477848f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5b3a84fbc42c4e86"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d44a6aefa6b4c5b"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re561cb0a04a64723"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5b3a84fbc42c4e86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R87048754754247ba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re561cb0a04a64723"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c37673bc93a4b27"/>
 </x:worksheet>
 </file>